--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -19,14 +19,13 @@
     <sheet sheetId="13" name="Approvals" state="visible" r:id="rId16"/>
     <sheet sheetId="14" name="Skills" state="visible" r:id="rId17"/>
     <sheet sheetId="15" name="Hand-overs" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="Adapted this cycle" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6017" uniqueCount="1640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6015" uniqueCount="1639">
   <si>
     <t>Metric</t>
   </si>
@@ -178,7 +177,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-11T16:15:28.529Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-11T16:44:18.965Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4730,7 +4729,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:15:29.184Z</t>
+    <t>2026-10-11T16:44:19.656Z</t>
   </si>
   <si>
     <t>118 requirements approved; 10 excluded (gaps AQPI-8, AQPI-13, AQPI-22); 0 conflict(s) resolved</t>
@@ -4986,9 +4985,6 @@
   </si>
   <si>
     <t>cycleReport: delivered; comparison: n/a; testCaseExport: delivered</t>
-  </si>
-  <si>
-    <t>Lesson applied</t>
   </si>
 </sst>
 </file>
@@ -12219,29 +12215,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="110" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1639</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1549</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
@@ -22817,7 +22790,7 @@
         <v>1202</v>
       </c>
       <c r="E2" s="2">
-        <v>548</v>
+        <v>494</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -22960,7 +22933,7 @@
         <v>1202</v>
       </c>
       <c r="E9" s="2">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -22979,7 +22952,7 @@
         <v>1202</v>
       </c>
       <c r="E10" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -22998,7 +22971,7 @@
         <v>1202</v>
       </c>
       <c r="E11" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -23017,7 +22990,7 @@
         <v>1202</v>
       </c>
       <c r="E12" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -23036,7 +23009,7 @@
         <v>1202</v>
       </c>
       <c r="E13" s="2">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -23118,7 +23091,7 @@
         <v>1202</v>
       </c>
       <c r="E17" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23137,7 +23110,7 @@
         <v>1202</v>
       </c>
       <c r="E18" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -23198,7 +23171,7 @@
         <v>1202</v>
       </c>
       <c r="E21" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -23238,7 +23211,7 @@
         <v>1202</v>
       </c>
       <c r="E23" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -23257,7 +23230,7 @@
         <v>1202</v>
       </c>
       <c r="E24" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -23276,7 +23249,7 @@
         <v>1202</v>
       </c>
       <c r="E25" s="2">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -23295,7 +23268,7 @@
         <v>1202</v>
       </c>
       <c r="E26" s="2">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -23314,7 +23287,7 @@
         <v>1202</v>
       </c>
       <c r="E27" s="2">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -23333,7 +23306,7 @@
         <v>1202</v>
       </c>
       <c r="E28" s="2">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -23352,7 +23325,7 @@
         <v>1202</v>
       </c>
       <c r="E29" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -23413,7 +23386,7 @@
         <v>1202</v>
       </c>
       <c r="E32" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -23453,7 +23426,7 @@
         <v>1202</v>
       </c>
       <c r="E34" s="2">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -23472,7 +23445,7 @@
         <v>1202</v>
       </c>
       <c r="E35" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -23575,7 +23548,7 @@
         <v>1202</v>
       </c>
       <c r="E40" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -23594,7 +23567,7 @@
         <v>1202</v>
       </c>
       <c r="E41" s="2">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -23613,7 +23586,7 @@
         <v>1202</v>
       </c>
       <c r="E42" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -23632,7 +23605,7 @@
         <v>1202</v>
       </c>
       <c r="E43" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -23756,7 +23729,7 @@
         <v>1202</v>
       </c>
       <c r="E49" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -23815,7 +23788,7 @@
         <v>1202</v>
       </c>
       <c r="E52" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -23918,7 +23891,7 @@
         <v>1202</v>
       </c>
       <c r="E57" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -24017,7 +23990,7 @@
         <v>1202</v>
       </c>
       <c r="E62" s="2">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -24036,7 +24009,7 @@
         <v>1202</v>
       </c>
       <c r="E63" s="2">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -24055,7 +24028,7 @@
         <v>1202</v>
       </c>
       <c r="E64" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -24095,7 +24068,7 @@
         <v>1202</v>
       </c>
       <c r="E66" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -24114,7 +24087,7 @@
         <v>1202</v>
       </c>
       <c r="E67" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -24133,7 +24106,7 @@
         <v>1202</v>
       </c>
       <c r="E68" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -24213,7 +24186,7 @@
         <v>1202</v>
       </c>
       <c r="E72" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -24251,7 +24224,7 @@
         <v>1202</v>
       </c>
       <c r="E74" s="2">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -24333,7 +24306,7 @@
         <v>1202</v>
       </c>
       <c r="E78" s="2">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -24352,7 +24325,7 @@
         <v>1202</v>
       </c>
       <c r="E79" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -24432,7 +24405,7 @@
         <v>1202</v>
       </c>
       <c r="E83" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -24514,7 +24487,7 @@
         <v>1202</v>
       </c>
       <c r="E87" s="2">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -24638,7 +24611,7 @@
         <v>1202</v>
       </c>
       <c r="E93" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -24678,7 +24651,7 @@
         <v>1202</v>
       </c>
       <c r="E95" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -24823,7 +24796,7 @@
         <v>1202</v>
       </c>
       <c r="E102" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -24905,7 +24878,7 @@
         <v>1202</v>
       </c>
       <c r="E106" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -24924,7 +24897,7 @@
         <v>1202</v>
       </c>
       <c r="E107" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -24943,7 +24916,7 @@
         <v>1205</v>
       </c>
       <c r="E108" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -24962,7 +24935,7 @@
         <v>1202</v>
       </c>
       <c r="E109" s="2">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -24981,7 +24954,7 @@
         <v>1202</v>
       </c>
       <c r="E110" s="2">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -25000,7 +24973,7 @@
         <v>1205</v>
       </c>
       <c r="E111" s="2">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -25019,7 +24992,7 @@
         <v>1202</v>
       </c>
       <c r="E112" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -25038,7 +25011,7 @@
         <v>1202</v>
       </c>
       <c r="E113" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25057,7 +25030,7 @@
         <v>1202</v>
       </c>
       <c r="E114" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25076,7 +25049,7 @@
         <v>1202</v>
       </c>
       <c r="E115" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -25095,7 +25068,7 @@
         <v>1202</v>
       </c>
       <c r="E116" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -25114,7 +25087,7 @@
         <v>1202</v>
       </c>
       <c r="E117" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -25133,7 +25106,7 @@
         <v>1202</v>
       </c>
       <c r="E118" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -25152,7 +25125,7 @@
         <v>1202</v>
       </c>
       <c r="E119" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -25171,7 +25144,7 @@
         <v>1205</v>
       </c>
       <c r="E120" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -25190,7 +25163,7 @@
         <v>1202</v>
       </c>
       <c r="E121" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -25209,7 +25182,7 @@
         <v>1202</v>
       </c>
       <c r="E122" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6015" uniqueCount="1639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6015" uniqueCount="1641">
   <si>
     <t>Metric</t>
   </si>
@@ -177,7 +177,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-11T16:44:18.965Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-11T17:06:49.303Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3736,13 +3736,13 @@
     <t>AQPI-8</t>
   </si>
   <si>
-    <t>not raised in Jira</t>
-  </si>
-  <si>
-    <t>Code implements AQPI-8 (4 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-8</t>
+    <t>not raised in Jira; linked to AQPI-8 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-8 4.2 Sort and filter hotel results (4 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-8</t>
   </si>
   <si>
     <t>DEF-005</t>
@@ -3754,10 +3754,13 @@
     <t>AQPI-13</t>
   </si>
   <si>
-    <t>Code implements AQPI-13 (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-13</t>
+    <t>not raised in Jira; linked to AQPI-13 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-13 5.3 Explain and control personalization (3 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-13</t>
   </si>
   <si>
     <t>DEF-006</t>
@@ -3769,10 +3772,13 @@
     <t>AQPI-22</t>
   </si>
   <si>
-    <t>Code implements AQPI-22 (3 acceptance criteria)</t>
-  </si>
-  <si>
-    <t>No code in demo/hotel-booking-platform mentions AQPI-22</t>
+    <t>not raised in Jira; linked to AQPI-22 in the platform</t>
+  </si>
+  <si>
+    <t>The code implements AQPI-22 7.4 Show booking outcome (3 acceptance criteria)</t>
+  </si>
+  <si>
+    <t>No code in sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) mentions AQPI-22</t>
   </si>
   <si>
     <t>DEF-007</t>
@@ -4729,7 +4735,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:19.656Z</t>
+    <t>2026-10-11T17:06:49.939Z</t>
   </si>
   <si>
     <t>118 requirements approved; 10 excluded (gaps AQPI-8, AQPI-13, AQPI-22); 0 conflict(s) resolved</t>
@@ -5579,19 +5585,19 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
@@ -5620,16 +5626,16 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="F2" s="2">
         <v>2</v>
@@ -5650,24 +5656,24 @@
         <v>71</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="F3" s="2">
         <v>4</v>
@@ -5688,7 +5694,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5696,16 +5702,16 @@
         <v>120</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="F4" s="2">
         <v>7</v>
@@ -5726,7 +5732,7 @@
         <v>71</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5734,16 +5740,16 @@
         <v>150</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="F5" s="2">
         <v>7</v>
@@ -5761,10 +5767,10 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5772,16 +5778,16 @@
         <v>171</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -5802,24 +5808,24 @@
         <v>71</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F7" s="2">
         <v>4</v>
@@ -5840,7 +5846,7 @@
         <v>71</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5848,16 +5854,16 @@
         <v>183</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
@@ -5878,7 +5884,7 @@
         <v>71</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5886,16 +5892,16 @@
         <v>1221</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="F9" s="2">
         <v>0</v>
@@ -5916,7 +5922,7 @@
         <v>71</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5924,16 +5930,16 @@
         <v>204</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="F10" s="2">
         <v>4</v>
@@ -5954,24 +5960,24 @@
         <v>71</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
@@ -5992,7 +5998,7 @@
         <v>71</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6000,16 +6006,16 @@
         <v>221</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="F12" s="2">
         <v>7</v>
@@ -6030,7 +6036,7 @@
         <v>71</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6038,16 +6044,16 @@
         <v>250</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
@@ -6068,7 +6074,7 @@
         <v>71</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6076,16 +6082,16 @@
         <v>1227</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -6106,24 +6112,24 @@
         <v>71</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
@@ -6144,7 +6150,7 @@
         <v>71</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6152,16 +6158,16 @@
         <v>265</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
@@ -6182,7 +6188,7 @@
         <v>71</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6190,16 +6196,16 @@
         <v>286</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -6220,7 +6226,7 @@
         <v>71</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6228,16 +6234,16 @@
         <v>303</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="F18" s="2">
         <v>6</v>
@@ -6255,27 +6261,27 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="F19" s="2">
         <v>4</v>
@@ -6296,7 +6302,7 @@
         <v>71</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6304,16 +6310,16 @@
         <v>324</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
@@ -6334,7 +6340,7 @@
         <v>71</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6342,16 +6348,16 @@
         <v>349</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="F21" s="2">
         <v>6</v>
@@ -6372,7 +6378,7 @@
         <v>71</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6380,16 +6386,16 @@
         <v>374</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="F22" s="2">
         <v>7</v>
@@ -6407,27 +6413,27 @@
         <v>1</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
@@ -6448,24 +6454,24 @@
         <v>71</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="F24" s="2">
         <v>4</v>
@@ -6486,7 +6492,7 @@
         <v>71</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6494,16 +6500,16 @@
         <v>399</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="F25" s="2">
         <v>4</v>
@@ -6524,7 +6530,7 @@
         <v>71</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6532,16 +6538,16 @@
         <v>418</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="F26" s="2">
         <v>5</v>
@@ -6562,7 +6568,7 @@
         <v>71</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6570,16 +6576,16 @@
         <v>439</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -6600,24 +6606,24 @@
         <v>71</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
@@ -6638,7 +6644,7 @@
         <v>71</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6646,16 +6652,16 @@
         <v>452</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="F29" s="2">
         <v>5</v>
@@ -6676,7 +6682,7 @@
         <v>71</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="30" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6684,16 +6690,16 @@
         <v>472</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="F30" s="2">
         <v>5</v>
@@ -6714,7 +6720,7 @@
         <v>71</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="31" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6722,16 +6728,16 @@
         <v>497</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="F31" s="2">
         <v>3</v>
@@ -6752,7 +6758,7 @@
         <v>71</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6760,16 +6766,16 @@
         <v>514</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
@@ -6790,7 +6796,7 @@
         <v>71</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -6825,13 +6831,13 @@
         <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>567</v>
@@ -6840,19 +6846,19 @@
         <v>54</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1198</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>1209</v>
@@ -6884,10 +6890,10 @@
         <v>590</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>1202</v>
@@ -6925,7 +6931,7 @@
         <v>601</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
@@ -6964,7 +6970,7 @@
         <v>601</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
@@ -7003,7 +7009,7 @@
         <v>601</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
@@ -7042,7 +7048,7 @@
         <v>601</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
@@ -7081,7 +7087,7 @@
         <v>601</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
@@ -7120,10 +7126,10 @@
         <v>590</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>1202</v>
@@ -7161,10 +7167,10 @@
         <v>590</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>1202</v>
@@ -7202,10 +7208,10 @@
         <v>590</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>1202</v>
@@ -7243,10 +7249,10 @@
         <v>590</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>1202</v>
@@ -7284,10 +7290,10 @@
         <v>590</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>1378</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>1376</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>1202</v>
@@ -7325,10 +7331,10 @@
         <v>590</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>1202</v>
@@ -7366,7 +7372,7 @@
         <v>601</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
@@ -7405,7 +7411,7 @@
         <v>601</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
@@ -7444,7 +7450,7 @@
         <v>601</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
@@ -7483,10 +7489,10 @@
         <v>590</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>1202</v>
@@ -7524,10 +7530,10 @@
         <v>590</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>1202</v>
@@ -7565,7 +7571,7 @@
         <v>601</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
@@ -7604,7 +7610,7 @@
         <v>601</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
@@ -7643,10 +7649,10 @@
         <v>590</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>1202</v>
@@ -7684,7 +7690,7 @@
         <v>601</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
@@ -7723,10 +7729,10 @@
         <v>590</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>1202</v>
@@ -7764,10 +7770,10 @@
         <v>590</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>1202</v>
@@ -7805,10 +7811,10 @@
         <v>590</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>1202</v>
@@ -7846,10 +7852,10 @@
         <v>590</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>1202</v>
@@ -7887,10 +7893,10 @@
         <v>590</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>1202</v>
@@ -7928,10 +7934,10 @@
         <v>590</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>1202</v>
@@ -7969,10 +7975,10 @@
         <v>590</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>1202</v>
@@ -8010,7 +8016,7 @@
         <v>601</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
@@ -8049,7 +8055,7 @@
         <v>601</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
@@ -8088,10 +8094,10 @@
         <v>590</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>1202</v>
@@ -8129,7 +8135,7 @@
         <v>601</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
@@ -8168,10 +8174,10 @@
         <v>590</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>1202</v>
@@ -8209,10 +8215,10 @@
         <v>590</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>1202</v>
@@ -8250,7 +8256,7 @@
         <v>601</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
@@ -8289,7 +8295,7 @@
         <v>601</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
@@ -8328,7 +8334,7 @@
         <v>601</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
@@ -8367,7 +8373,7 @@
         <v>601</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
@@ -8406,10 +8412,10 @@
         <v>590</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>1202</v>
@@ -8447,10 +8453,10 @@
         <v>590</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>1202</v>
@@ -8488,10 +8494,10 @@
         <v>590</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>1202</v>
@@ -8529,10 +8535,10 @@
         <v>590</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>1202</v>
@@ -8570,7 +8576,7 @@
         <v>601</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
@@ -8609,7 +8615,7 @@
         <v>601</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
@@ -8648,7 +8654,7 @@
         <v>601</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
@@ -8687,7 +8693,7 @@
         <v>601</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
@@ -8726,7 +8732,7 @@
         <v>601</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
@@ -8765,10 +8771,10 @@
         <v>590</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>1202</v>
@@ -8806,10 +8812,10 @@
         <v>590</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>1202</v>
@@ -8847,7 +8853,7 @@
         <v>601</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
@@ -8886,10 +8892,10 @@
         <v>590</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>1202</v>
@@ -8927,7 +8933,7 @@
         <v>601</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -8966,7 +8972,7 @@
         <v>601</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -9005,7 +9011,7 @@
         <v>601</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -9044,7 +9050,7 @@
         <v>601</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -9083,10 +9089,10 @@
         <v>590</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>1202</v>
@@ -9124,10 +9130,10 @@
         <v>590</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>1202</v>
@@ -9165,10 +9171,10 @@
         <v>590</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>1202</v>
@@ -9206,7 +9212,7 @@
         <v>601</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
@@ -9245,7 +9251,7 @@
         <v>601</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
@@ -9284,10 +9290,10 @@
         <v>590</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>1202</v>
@@ -9325,10 +9331,10 @@
         <v>590</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>1202</v>
@@ -9366,10 +9372,10 @@
         <v>590</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>1202</v>
@@ -9407,7 +9413,7 @@
         <v>601</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -9446,10 +9452,10 @@
         <v>590</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>1202</v>
@@ -9487,10 +9493,10 @@
         <v>590</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>1202</v>
@@ -9528,10 +9534,10 @@
         <v>590</v>
       </c>
       <c r="I68" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="J68" s="2" t="s">
         <v>1461</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>1459</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>1202</v>
@@ -9569,10 +9575,10 @@
         <v>590</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>1202</v>
@@ -9610,7 +9616,7 @@
         <v>601</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -9649,7 +9655,7 @@
         <v>601</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
@@ -9688,10 +9694,10 @@
         <v>590</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>1202</v>
@@ -9729,10 +9735,10 @@
         <v>590</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>1202</v>
@@ -9770,10 +9776,10 @@
         <v>590</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>1202</v>
@@ -9811,7 +9817,7 @@
         <v>601</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
@@ -9850,7 +9856,7 @@
         <v>601</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -9889,7 +9895,7 @@
         <v>601</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
@@ -9928,10 +9934,10 @@
         <v>590</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>1202</v>
@@ -9969,10 +9975,10 @@
         <v>590</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>1202</v>
@@ -10010,7 +10016,7 @@
         <v>601</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -10049,10 +10055,10 @@
         <v>590</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1202</v>
@@ -10090,7 +10096,7 @@
         <v>601</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -10129,10 +10135,10 @@
         <v>590</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>1202</v>
@@ -10170,7 +10176,7 @@
         <v>601</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -10209,7 +10215,7 @@
         <v>601</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -10248,7 +10254,7 @@
         <v>601</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -10287,10 +10293,10 @@
         <v>590</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>1202</v>
@@ -10328,7 +10334,7 @@
         <v>601</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
@@ -10367,7 +10373,7 @@
         <v>601</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
@@ -10406,7 +10412,7 @@
         <v>601</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
@@ -10445,7 +10451,7 @@
         <v>601</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2" t="s">
@@ -10484,7 +10490,7 @@
         <v>601</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="J92" s="2"/>
       <c r="K92" s="2" t="s">
@@ -10523,10 +10529,10 @@
         <v>590</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>1202</v>
@@ -10564,7 +10570,7 @@
         <v>601</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
@@ -10603,10 +10609,10 @@
         <v>590</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>1202</v>
@@ -10644,7 +10650,7 @@
         <v>601</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -10683,7 +10689,7 @@
         <v>601</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -10722,7 +10728,7 @@
         <v>601</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="J98" s="2"/>
       <c r="K98" s="2" t="s">
@@ -10761,7 +10767,7 @@
         <v>601</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="J99" s="2"/>
       <c r="K99" s="2" t="s">
@@ -10800,7 +10806,7 @@
         <v>601</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2" t="s">
@@ -10839,7 +10845,7 @@
         <v>601</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -10878,10 +10884,10 @@
         <v>590</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>1202</v>
@@ -10919,7 +10925,7 @@
         <v>601</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="J103" s="2"/>
       <c r="K103" s="2" t="s">
@@ -10958,7 +10964,7 @@
         <v>601</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
@@ -10997,7 +11003,7 @@
         <v>601</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="J105" s="2"/>
       <c r="K105" s="2" t="s">
@@ -11036,10 +11042,10 @@
         <v>590</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>1202</v>
@@ -11077,10 +11083,10 @@
         <v>590</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>1202</v>
@@ -11118,16 +11124,16 @@
         <v>590</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K108" s="2" t="s">
         <v>1205</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>71</v>
@@ -11159,10 +11165,10 @@
         <v>590</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>1202</v>
@@ -11200,10 +11206,10 @@
         <v>590</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>1202</v>
@@ -11241,16 +11247,16 @@
         <v>590</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K111" s="2" t="s">
         <v>1205</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>71</v>
@@ -11282,10 +11288,10 @@
         <v>590</v>
       </c>
       <c r="I112" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J112" s="2" t="s">
         <v>1521</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>1519</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>1202</v>
@@ -11323,10 +11329,10 @@
         <v>590</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>1202</v>
@@ -11364,10 +11370,10 @@
         <v>590</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>1202</v>
@@ -11405,10 +11411,10 @@
         <v>590</v>
       </c>
       <c r="I115" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="J115" s="2" t="s">
         <v>1525</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>1523</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>1202</v>
@@ -11446,10 +11452,10 @@
         <v>590</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>1202</v>
@@ -11487,10 +11493,10 @@
         <v>590</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>1202</v>
@@ -11528,10 +11534,10 @@
         <v>590</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>1202</v>
@@ -11569,10 +11575,10 @@
         <v>590</v>
       </c>
       <c r="I119" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="J119" s="2" t="s">
         <v>1530</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>1528</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>1202</v>
@@ -11610,16 +11616,16 @@
         <v>590</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>1205</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="M120" s="2" t="s">
         <v>71</v>
@@ -11651,10 +11657,10 @@
         <v>590</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>1202</v>
@@ -11692,10 +11698,10 @@
         <v>590</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>1202</v>
@@ -11731,40 +11737,40 @@
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>1200</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
   </sheetData>
@@ -11787,36 +11793,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
   </sheetData>
@@ -11839,189 +11845,189 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>567</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
     </row>
   </sheetData>
@@ -12044,169 +12050,169 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
     </row>
   </sheetData>
@@ -22790,7 +22796,7 @@
         <v>1202</v>
       </c>
       <c r="E2" s="2">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -22914,7 +22920,7 @@
         <v>1202</v>
       </c>
       <c r="E8" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -22933,7 +22939,7 @@
         <v>1202</v>
       </c>
       <c r="E9" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -22952,7 +22958,7 @@
         <v>1202</v>
       </c>
       <c r="E10" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -22971,7 +22977,7 @@
         <v>1202</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -23091,7 +23097,7 @@
         <v>1202</v>
       </c>
       <c r="E17" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23171,7 +23177,7 @@
         <v>1202</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -23211,7 +23217,7 @@
         <v>1202</v>
       </c>
       <c r="E23" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -23249,7 +23255,7 @@
         <v>1202</v>
       </c>
       <c r="E25" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -23268,7 +23274,7 @@
         <v>1202</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -23287,7 +23293,7 @@
         <v>1202</v>
       </c>
       <c r="E27" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -23306,7 +23312,7 @@
         <v>1202</v>
       </c>
       <c r="E28" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -23325,7 +23331,7 @@
         <v>1202</v>
       </c>
       <c r="E29" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -23426,7 +23432,7 @@
         <v>1202</v>
       </c>
       <c r="E34" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -23445,7 +23451,7 @@
         <v>1202</v>
       </c>
       <c r="E35" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -23567,7 +23573,7 @@
         <v>1202</v>
       </c>
       <c r="E41" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -23586,7 +23592,7 @@
         <v>1202</v>
       </c>
       <c r="E42" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -23729,7 +23735,7 @@
         <v>1202</v>
       </c>
       <c r="E49" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -23788,7 +23794,7 @@
         <v>1202</v>
       </c>
       <c r="E52" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -23891,7 +23897,7 @@
         <v>1202</v>
       </c>
       <c r="E57" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -23929,7 +23935,7 @@
         <v>1202</v>
       </c>
       <c r="E59" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -23990,7 +23996,7 @@
         <v>1202</v>
       </c>
       <c r="E62" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -24009,7 +24015,7 @@
         <v>1202</v>
       </c>
       <c r="E63" s="2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -24028,7 +24034,7 @@
         <v>1202</v>
       </c>
       <c r="E64" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -24068,7 +24074,7 @@
         <v>1202</v>
       </c>
       <c r="E66" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -24087,7 +24093,7 @@
         <v>1202</v>
       </c>
       <c r="E67" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -24106,7 +24112,7 @@
         <v>1202</v>
       </c>
       <c r="E68" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -24125,7 +24131,7 @@
         <v>1202</v>
       </c>
       <c r="E69" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -24186,7 +24192,7 @@
         <v>1202</v>
       </c>
       <c r="E72" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -24205,7 +24211,7 @@
         <v>1202</v>
       </c>
       <c r="E73" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -24224,7 +24230,7 @@
         <v>1202</v>
       </c>
       <c r="E74" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -24306,7 +24312,7 @@
         <v>1202</v>
       </c>
       <c r="E78" s="2">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -24325,7 +24331,7 @@
         <v>1202</v>
       </c>
       <c r="E79" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -24365,7 +24371,7 @@
         <v>1202</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -24405,7 +24411,7 @@
         <v>1202</v>
       </c>
       <c r="E83" s="2">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -24487,7 +24493,7 @@
         <v>1202</v>
       </c>
       <c r="E87" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -24651,7 +24657,7 @@
         <v>1202</v>
       </c>
       <c r="E95" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -24796,7 +24802,7 @@
         <v>1202</v>
       </c>
       <c r="E102" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -24878,7 +24884,7 @@
         <v>1202</v>
       </c>
       <c r="E106" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -24897,7 +24903,7 @@
         <v>1202</v>
       </c>
       <c r="E107" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -24916,7 +24922,7 @@
         <v>1205</v>
       </c>
       <c r="E108" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -24935,7 +24941,7 @@
         <v>1202</v>
       </c>
       <c r="E109" s="2">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -24954,7 +24960,7 @@
         <v>1202</v>
       </c>
       <c r="E110" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -24973,7 +24979,7 @@
         <v>1205</v>
       </c>
       <c r="E111" s="2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -24992,7 +24998,7 @@
         <v>1202</v>
       </c>
       <c r="E112" s="2">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -25011,7 +25017,7 @@
         <v>1202</v>
       </c>
       <c r="E113" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25030,7 +25036,7 @@
         <v>1202</v>
       </c>
       <c r="E114" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25049,7 +25055,7 @@
         <v>1202</v>
       </c>
       <c r="E115" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -25068,7 +25074,7 @@
         <v>1202</v>
       </c>
       <c r="E116" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -25087,7 +25093,7 @@
         <v>1202</v>
       </c>
       <c r="E117" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -25106,7 +25112,7 @@
         <v>1202</v>
       </c>
       <c r="E118" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -25125,7 +25131,7 @@
         <v>1202</v>
       </c>
       <c r="E119" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -25144,7 +25150,7 @@
         <v>1205</v>
       </c>
       <c r="E120" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -25163,7 +25169,7 @@
         <v>1202</v>
       </c>
       <c r="E121" s="2">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -25182,7 +25188,7 @@
         <v>1202</v>
       </c>
       <c r="E122" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -25304,15 +25310,15 @@
         <v>1227</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>73</v>
@@ -25324,27 +25330,27 @@
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1220</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1222</v>
+        <v>1234</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>73</v>
@@ -25356,19 +25362,19 @@
     </row>
     <row r="5" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>1111</v>
@@ -25377,13 +25383,13 @@
         <v>536</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>73</v>
@@ -25395,10 +25401,10 @@
     </row>
     <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>624</v>
@@ -25407,7 +25413,7 @@
         <v>374</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>1129</v>
@@ -25416,13 +25422,13 @@
         <v>546</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>73</v>
@@ -25434,10 +25440,10 @@
     </row>
     <row r="7" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>624</v>
@@ -25446,7 +25452,7 @@
         <v>150</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>1179</v>
@@ -25455,13 +25461,13 @@
         <v>556</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>73</v>
@@ -25503,10 +25509,10 @@
         <v>1197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1198</v>
@@ -25515,7 +25521,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
@@ -25542,16 +25548,16 @@
         <v>53</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>590</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>23</v>
@@ -25580,7 +25586,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="3" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25603,7 +25609,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25626,7 +25632,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25649,7 +25655,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25672,7 +25678,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25695,7 +25701,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25718,7 +25724,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25741,7 +25747,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25764,7 +25770,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25787,7 +25793,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25810,7 +25816,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25833,7 +25839,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25856,7 +25862,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25879,7 +25885,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25902,7 +25908,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25925,7 +25931,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25948,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25971,7 +25977,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -25994,7 +26000,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26017,7 +26023,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26040,7 +26046,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26063,7 +26069,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26086,7 +26092,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26109,7 +26115,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26132,7 +26138,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26155,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26178,7 +26184,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26201,7 +26207,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26224,7 +26230,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26247,7 +26253,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26270,7 +26276,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26293,7 +26299,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26316,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26339,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26362,7 +26368,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26385,7 +26391,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26408,7 +26414,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26431,7 +26437,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26454,7 +26460,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26477,7 +26483,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26500,7 +26506,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26523,7 +26529,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26546,7 +26552,7 @@
         <v>0</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26569,7 +26575,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26592,7 +26598,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26615,7 +26621,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26638,7 +26644,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26661,7 +26667,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26684,7 +26690,7 @@
         <v>0</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26707,7 +26713,7 @@
         <v>0</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26730,7 +26736,7 @@
         <v>0</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26753,7 +26759,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26776,7 +26782,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26799,7 +26805,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26822,7 +26828,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26845,7 +26851,7 @@
         <v>0</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="58" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26868,7 +26874,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="59" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26891,7 +26897,7 @@
         <v>0</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="60" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26914,7 +26920,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="61" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26937,7 +26943,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="62" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26960,7 +26966,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="63" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -26983,7 +26989,7 @@
         <v>0</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="64" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27006,7 +27012,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="65" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27029,7 +27035,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="66" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27052,7 +27058,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="67" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27075,7 +27081,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="68" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27098,7 +27104,7 @@
         <v>0</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="69" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27121,7 +27127,7 @@
         <v>0</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="70" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27144,7 +27150,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="71" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27167,7 +27173,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="72" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27190,7 +27196,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="73" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27213,7 +27219,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="74" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27236,7 +27242,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="75" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27259,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="76" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27282,7 +27288,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27305,7 +27311,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="78" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27328,7 +27334,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27351,7 +27357,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27374,7 +27380,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27397,7 +27403,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27420,7 +27426,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27443,7 +27449,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27466,7 +27472,7 @@
         <v>0</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27489,7 +27495,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27512,7 +27518,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27535,7 +27541,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27558,7 +27564,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27581,7 +27587,7 @@
         <v>0</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27604,7 +27610,7 @@
         <v>0</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27627,7 +27633,7 @@
         <v>0</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27650,7 +27656,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27673,7 +27679,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27696,7 +27702,7 @@
         <v>0</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27719,7 +27725,7 @@
         <v>0</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27742,7 +27748,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27765,7 +27771,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27788,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27811,7 +27817,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27834,7 +27840,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="101" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27857,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="102" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27880,7 +27886,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="103" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27903,7 +27909,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="104" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27926,7 +27932,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="105" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27949,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="106" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27972,7 +27978,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="107" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -27995,7 +28001,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="108" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28018,7 +28024,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="109" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28041,7 +28047,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="110" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28064,7 +28070,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="111" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28087,7 +28093,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="112" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28110,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="113" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28133,7 +28139,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="114" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28156,7 +28162,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="115" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28179,7 +28185,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="116" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28202,7 +28208,7 @@
         <v>1</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="117" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28225,7 +28231,7 @@
         <v>0</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="118" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28248,7 +28254,7 @@
         <v>1</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -28271,7 +28277,7 @@
         <v>0</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
     </row>
   </sheetData>
@@ -28293,13 +28299,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
@@ -28307,212 +28313,212 @@
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>1280</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1173</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>828</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>880</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
     </row>
   </sheetData>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -42,7 +42,7 @@
     <t>Cycle</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (CYC-2, baseline)</t>
+    <t>Hotel booking baseline · DQE (CYC-2, baseline)</t>
   </si>
   <si>
     <t>Status</t>
@@ -87,7 +87,7 @@
     <t>{"functional":238,"automation":65,"non-functional":4}</t>
   </si>
   <si>
-    <t>Scripts</t>
+    <t>Automation scripts</t>
   </si>
   <si>
     <t>Executed (real)</t>
@@ -117,7 +117,7 @@
     <t>Narrative</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) (pulled live from GitHub). The reviewed requirement set holds 118 requirements. 121 test cases are designed, 65 of them automated in 50 Playwright scripts. Execution ran 65 automated cases for real: 62 passed and 3 failed (pass rate 95.4%). 6 defect(s) were raised from real failures: DEF-004 AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code; DEF-005 AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code; DEF-006 AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code; DEF-007 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-008 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-009 9 rooms in one search are rejected: returns 200 instead of 400.</t>
+    <t>Hotel booking baseline · DQE (baseline) worked from Jira initiative AQPI-1 (Jira export on GitHub), Jira epic AQPI-2, AQPI-6, AQPI-10, AQPI-14, AQPI-18, AQPI-23, AQPI-27 (Jira export on GitHub), Codebase sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) (pulled live from GitHub). The reviewed requirement set holds 118 requirements. 121 test cases are designed, 65 of them automated in 50 Playwright scripts. Execution ran 65 automated cases for real: 62 passed and 3 failed (pass rate 95.4%). 6 defect(s) were raised from real failures: DEF-004 AQPI-8 4.2 Sort and filter hotel results: asked for in Jira but not implemented in the code; DEF-005 AQPI-13 5.3 Explain and control personalization: asked for in Jira but not implemented in the code; DEF-006 AQPI-22 7.4 Show booking outcome: asked for in Jira but not implemented in the code; DEF-007 A price change within 1% does not need acknowledgement: returns true instead of false; DEF-008 A key shorter than 8 characters is refused: returns 201 instead of 400; DEF-009 9 rooms in one search are rejected: returns 200 instead of 400.</t>
   </si>
   <si>
     <t>Narrative drafted by</t>
@@ -177,7 +177,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-11T17:06:49.303Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-12T01:35:07.891Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1801,7 +1801,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Hotel booking baseline · Functional</t>
+    <t>Hotel booking baseline · DQE</t>
   </si>
   <si>
     <t>TC-F-002</t>
@@ -4735,7 +4735,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-11T17:06:49.939Z</t>
+    <t>2026-10-12T01:35:08.490Z</t>
   </si>
   <si>
     <t>118 requirements approved; 10 excluded (gaps AQPI-8, AQPI-13, AQPI-22); 0 conflict(s) resolved</t>
@@ -4873,7 +4873,7 @@
     <t>testing-functional</t>
   </si>
   <si>
-    <t>Functional testing</t>
+    <t>DQE testing (domain functional)</t>
   </si>
   <si>
     <t>Steers the design agents to cover every business rule and its boundaries through the service API.</t>
@@ -22796,7 +22796,7 @@
         <v>1202</v>
       </c>
       <c r="E2" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -22920,7 +22920,7 @@
         <v>1202</v>
       </c>
       <c r="E8" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -22939,7 +22939,7 @@
         <v>1202</v>
       </c>
       <c r="E9" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -22958,7 +22958,7 @@
         <v>1202</v>
       </c>
       <c r="E10" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -22977,7 +22977,7 @@
         <v>1202</v>
       </c>
       <c r="E11" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -22996,7 +22996,7 @@
         <v>1202</v>
       </c>
       <c r="E12" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -23015,7 +23015,7 @@
         <v>1202</v>
       </c>
       <c r="E13" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -23097,7 +23097,7 @@
         <v>1202</v>
       </c>
       <c r="E17" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23177,7 +23177,7 @@
         <v>1202</v>
       </c>
       <c r="E21" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -23217,7 +23217,7 @@
         <v>1202</v>
       </c>
       <c r="E23" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -23236,7 +23236,7 @@
         <v>1202</v>
       </c>
       <c r="E24" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -23255,7 +23255,7 @@
         <v>1202</v>
       </c>
       <c r="E25" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -23274,7 +23274,7 @@
         <v>1202</v>
       </c>
       <c r="E26" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -23293,7 +23293,7 @@
         <v>1202</v>
       </c>
       <c r="E27" s="2">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -23331,7 +23331,7 @@
         <v>1202</v>
       </c>
       <c r="E29" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -23392,7 +23392,7 @@
         <v>1202</v>
       </c>
       <c r="E32" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -23432,7 +23432,7 @@
         <v>1202</v>
       </c>
       <c r="E34" s="2">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -23451,7 +23451,7 @@
         <v>1202</v>
       </c>
       <c r="E35" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -23554,7 +23554,7 @@
         <v>1202</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -23573,7 +23573,7 @@
         <v>1202</v>
       </c>
       <c r="E41" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -23592,7 +23592,7 @@
         <v>1202</v>
       </c>
       <c r="E42" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -23611,7 +23611,7 @@
         <v>1202</v>
       </c>
       <c r="E43" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -23735,7 +23735,7 @@
         <v>1202</v>
       </c>
       <c r="E49" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -23754,7 +23754,7 @@
         <v>1202</v>
       </c>
       <c r="E50" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -23794,7 +23794,7 @@
         <v>1202</v>
       </c>
       <c r="E52" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -23916,7 +23916,7 @@
         <v>1202</v>
       </c>
       <c r="E58" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -23935,7 +23935,7 @@
         <v>1202</v>
       </c>
       <c r="E59" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -24034,7 +24034,7 @@
         <v>1202</v>
       </c>
       <c r="E64" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -24074,7 +24074,7 @@
         <v>1202</v>
       </c>
       <c r="E66" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -24093,7 +24093,7 @@
         <v>1202</v>
       </c>
       <c r="E67" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -24112,7 +24112,7 @@
         <v>1202</v>
       </c>
       <c r="E68" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -24131,7 +24131,7 @@
         <v>1202</v>
       </c>
       <c r="E69" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -24192,7 +24192,7 @@
         <v>1202</v>
       </c>
       <c r="E72" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -24211,7 +24211,7 @@
         <v>1202</v>
       </c>
       <c r="E73" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -24230,7 +24230,7 @@
         <v>1202</v>
       </c>
       <c r="E74" s="2">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -24312,7 +24312,7 @@
         <v>1202</v>
       </c>
       <c r="E78" s="2">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -24331,7 +24331,7 @@
         <v>1202</v>
       </c>
       <c r="E79" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -24371,7 +24371,7 @@
         <v>1202</v>
       </c>
       <c r="E81" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -24411,7 +24411,7 @@
         <v>1202</v>
       </c>
       <c r="E83" s="2">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -24493,7 +24493,7 @@
         <v>1202</v>
       </c>
       <c r="E87" s="2">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -24617,7 +24617,7 @@
         <v>1202</v>
       </c>
       <c r="E93" s="2">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -24657,7 +24657,7 @@
         <v>1202</v>
       </c>
       <c r="E95" s="2">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -24802,7 +24802,7 @@
         <v>1202</v>
       </c>
       <c r="E102" s="2">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -24884,7 +24884,7 @@
         <v>1202</v>
       </c>
       <c r="E106" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -24903,7 +24903,7 @@
         <v>1202</v>
       </c>
       <c r="E107" s="2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -24922,7 +24922,7 @@
         <v>1205</v>
       </c>
       <c r="E108" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -24941,7 +24941,7 @@
         <v>1202</v>
       </c>
       <c r="E109" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -24960,7 +24960,7 @@
         <v>1202</v>
       </c>
       <c r="E110" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -24979,7 +24979,7 @@
         <v>1205</v>
       </c>
       <c r="E111" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -24998,7 +24998,7 @@
         <v>1202</v>
       </c>
       <c r="E112" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -25017,7 +25017,7 @@
         <v>1202</v>
       </c>
       <c r="E113" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25036,7 +25036,7 @@
         <v>1202</v>
       </c>
       <c r="E114" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25055,7 +25055,7 @@
         <v>1202</v>
       </c>
       <c r="E115" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -25093,7 +25093,7 @@
         <v>1202</v>
       </c>
       <c r="E117" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -25112,7 +25112,7 @@
         <v>1202</v>
       </c>
       <c r="E118" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -25131,7 +25131,7 @@
         <v>1202</v>
       </c>
       <c r="E119" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -25150,7 +25150,7 @@
         <v>1205</v>
       </c>
       <c r="E120" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -25169,7 +25169,7 @@
         <v>1202</v>
       </c>
       <c r="E121" s="2">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -25188,7 +25188,7 @@
         <v>1202</v>
       </c>
       <c r="E122" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6015" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6020" uniqueCount="1645">
   <si>
     <t>Metric</t>
   </si>
@@ -177,7 +177,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-12T01:35:07.891Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-12T02:09:38.882Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -3380,7 +3380,7 @@
     <t>Verify a change above 1% needs acknowledgement before checkout.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 30% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 30% to 260.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -3406,7 +3406,7 @@
     <t>Verify a change within 1% is applied without blocking the guest.</t>
   </si>
   <si>
-    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate rises 0.5% after the cart is created.</t>
+    <t>The six hotel services are running with their seeded catalogue (reset before the case). The nightly rate is 200 when the cart is created and rises 0.5% to 201.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Create a cart
@@ -4735,7 +4735,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:08.490Z</t>
+    <t>2026-10-12T02:09:39.510Z</t>
   </si>
   <si>
     <t>118 requirements approved; 10 excluded (gaps AQPI-8, AQPI-13, AQPI-22); 0 conflict(s) resolved</t>
@@ -4840,6 +4840,18 @@
     <t>input-review.md</t>
   </si>
   <si>
+    <t>release-criteria</t>
+  </si>
+  <si>
+    <t>Release criteria (Go / Conditional go / No-go)</t>
+  </si>
+  <si>
+    <t>The parameters the cycle report applies to recommend Go, Conditional go or No-go. Edit this file, or upload a replacement, to change them without a code change.</t>
+  </si>
+  <si>
+    <t>release-criteria.md</t>
+  </si>
+  <si>
     <t>test-case-authoring</t>
   </si>
   <si>
@@ -4987,10 +4999,10 @@
     <t>Cycle report agent</t>
   </si>
   <si>
-    <t>cycle-report, test-case-authoring, traceability-handover</t>
-  </si>
-  <si>
-    <t>cycleReport: delivered; comparison: n/a; testCaseExport: delivered</t>
+    <t>cycle-report, release-criteria, test-case-authoring, traceability-handover</t>
+  </si>
+  <si>
+    <t>cycleReport: delivered; comparison: n/a; releaseDecision: delivered; testCaseExport: delivered</t>
   </si>
 </sst>
 </file>
@@ -11833,7 +11845,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -11973,61 +11985,78 @@
         <v>1592</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>1593</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>1595</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>1596</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>1597</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>1598</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1600</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>1601</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>1602</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>1603</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>1605</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>1606</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>1607</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>1608</v>
       </c>
-      <c r="E11" s="2" t="s">
+    </row>
+    <row r="12" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>1609</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1613</v>
       </c>
     </row>
   </sheetData>
@@ -12050,36 +12079,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1610</v>
+        <v>1614</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1611</v>
+        <v>1615</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1612</v>
+        <v>1616</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1613</v>
+        <v>1617</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>1615</v>
+        <v>1619</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1616</v>
+        <v>1620</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1618</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12087,132 +12116,132 @@
         <v>1585</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>1621</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>1617</v>
-      </c>
       <c r="D4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1622</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1624</v>
+        <v>1628</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1627</v>
+        <v>1631</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1628</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>1629</v>
+        <v>1633</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1630</v>
+        <v>1634</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1631</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>1632</v>
+        <v>1636</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1633</v>
+        <v>1637</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1634</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>1635</v>
+        <v>1639</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1636</v>
+        <v>1640</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1637</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>1638</v>
+        <v>1642</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1639</v>
+        <v>1643</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1640</v>
+        <v>1644</v>
       </c>
     </row>
   </sheetData>
@@ -22796,7 +22825,7 @@
         <v>1202</v>
       </c>
       <c r="E2" s="2">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -22920,7 +22949,7 @@
         <v>1202</v>
       </c>
       <c r="E8" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -22939,7 +22968,7 @@
         <v>1202</v>
       </c>
       <c r="E9" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -22958,7 +22987,7 @@
         <v>1202</v>
       </c>
       <c r="E10" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -22977,7 +23006,7 @@
         <v>1202</v>
       </c>
       <c r="E11" s="2">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -22996,7 +23025,7 @@
         <v>1202</v>
       </c>
       <c r="E12" s="2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -23015,7 +23044,7 @@
         <v>1202</v>
       </c>
       <c r="E13" s="2">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -23097,7 +23126,7 @@
         <v>1202</v>
       </c>
       <c r="E17" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23116,7 +23145,7 @@
         <v>1202</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -23177,7 +23206,7 @@
         <v>1202</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -23217,7 +23246,7 @@
         <v>1202</v>
       </c>
       <c r="E23" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -23236,7 +23265,7 @@
         <v>1202</v>
       </c>
       <c r="E24" s="2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -23255,7 +23284,7 @@
         <v>1202</v>
       </c>
       <c r="E25" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -23274,7 +23303,7 @@
         <v>1202</v>
       </c>
       <c r="E26" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -23293,7 +23322,7 @@
         <v>1202</v>
       </c>
       <c r="E27" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -23312,7 +23341,7 @@
         <v>1202</v>
       </c>
       <c r="E28" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -23331,7 +23360,7 @@
         <v>1202</v>
       </c>
       <c r="E29" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -23392,7 +23421,7 @@
         <v>1202</v>
       </c>
       <c r="E32" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -23432,7 +23461,7 @@
         <v>1202</v>
       </c>
       <c r="E34" s="2">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -23451,7 +23480,7 @@
         <v>1202</v>
       </c>
       <c r="E35" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -23573,7 +23602,7 @@
         <v>1202</v>
       </c>
       <c r="E41" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -23592,7 +23621,7 @@
         <v>1202</v>
       </c>
       <c r="E42" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -23611,7 +23640,7 @@
         <v>1202</v>
       </c>
       <c r="E43" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -23735,7 +23764,7 @@
         <v>1202</v>
       </c>
       <c r="E49" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -23794,7 +23823,7 @@
         <v>1202</v>
       </c>
       <c r="E52" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -23897,7 +23926,7 @@
         <v>1202</v>
       </c>
       <c r="E57" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -23916,7 +23945,7 @@
         <v>1202</v>
       </c>
       <c r="E58" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -23935,7 +23964,7 @@
         <v>1202</v>
       </c>
       <c r="E59" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -23996,7 +24025,7 @@
         <v>1202</v>
       </c>
       <c r="E62" s="2">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -24015,7 +24044,7 @@
         <v>1202</v>
       </c>
       <c r="E63" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -24034,7 +24063,7 @@
         <v>1202</v>
       </c>
       <c r="E64" s="2">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -24074,7 +24103,7 @@
         <v>1202</v>
       </c>
       <c r="E66" s="2">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -24093,7 +24122,7 @@
         <v>1202</v>
       </c>
       <c r="E67" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -24112,7 +24141,7 @@
         <v>1202</v>
       </c>
       <c r="E68" s="2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -24192,7 +24221,7 @@
         <v>1202</v>
       </c>
       <c r="E72" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -24211,7 +24240,7 @@
         <v>1202</v>
       </c>
       <c r="E73" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -24230,7 +24259,7 @@
         <v>1202</v>
       </c>
       <c r="E74" s="2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -24312,7 +24341,7 @@
         <v>1202</v>
       </c>
       <c r="E78" s="2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -24331,7 +24360,7 @@
         <v>1202</v>
       </c>
       <c r="E79" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -24371,7 +24400,7 @@
         <v>1202</v>
       </c>
       <c r="E81" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -24411,7 +24440,7 @@
         <v>1202</v>
       </c>
       <c r="E83" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -24493,7 +24522,7 @@
         <v>1202</v>
       </c>
       <c r="E87" s="2">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -24617,7 +24646,7 @@
         <v>1202</v>
       </c>
       <c r="E93" s="2">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -24657,7 +24686,7 @@
         <v>1202</v>
       </c>
       <c r="E95" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -24802,7 +24831,7 @@
         <v>1202</v>
       </c>
       <c r="E102" s="2">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -24884,7 +24913,7 @@
         <v>1202</v>
       </c>
       <c r="E106" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -24903,7 +24932,7 @@
         <v>1202</v>
       </c>
       <c r="E107" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -24922,7 +24951,7 @@
         <v>1205</v>
       </c>
       <c r="E108" s="2">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -24941,7 +24970,7 @@
         <v>1202</v>
       </c>
       <c r="E109" s="2">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -24960,7 +24989,7 @@
         <v>1202</v>
       </c>
       <c r="E110" s="2">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -24979,7 +25008,7 @@
         <v>1205</v>
       </c>
       <c r="E111" s="2">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -24998,7 +25027,7 @@
         <v>1202</v>
       </c>
       <c r="E112" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -25017,7 +25046,7 @@
         <v>1202</v>
       </c>
       <c r="E113" s="2">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25036,7 +25065,7 @@
         <v>1202</v>
       </c>
       <c r="E114" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25055,7 +25084,7 @@
         <v>1202</v>
       </c>
       <c r="E115" s="2">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -25074,7 +25103,7 @@
         <v>1202</v>
       </c>
       <c r="E116" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -25093,7 +25122,7 @@
         <v>1202</v>
       </c>
       <c r="E117" s="2">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -25112,7 +25141,7 @@
         <v>1202</v>
       </c>
       <c r="E118" s="2">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -25131,7 +25160,7 @@
         <v>1202</v>
       </c>
       <c r="E119" s="2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -25150,7 +25179,7 @@
         <v>1205</v>
       </c>
       <c r="E120" s="2">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -25169,7 +25198,7 @@
         <v>1202</v>
       </c>
       <c r="E121" s="2">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -25188,7 +25217,7 @@
         <v>1202</v>
       </c>
       <c r="E122" s="2">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-functional-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -177,7 +177,7 @@
     <t>github</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-12T02:09:38.882Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/hotel-booking-platform (b212a32) at 2026-10-12T02:21:57.385Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -4735,7 +4735,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-10-12T02:09:39.510Z</t>
+    <t>2026-10-12T02:21:58.035Z</t>
   </si>
   <si>
     <t>118 requirements approved; 10 excluded (gaps AQPI-8, AQPI-13, AQPI-22); 0 conflict(s) resolved</t>
@@ -22825,7 +22825,7 @@
         <v>1202</v>
       </c>
       <c r="E2" s="2">
-        <v>527</v>
+        <v>702</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -22949,7 +22949,7 @@
         <v>1202</v>
       </c>
       <c r="E8" s="2">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -22968,7 +22968,7 @@
         <v>1202</v>
       </c>
       <c r="E9" s="2">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -22987,7 +22987,7 @@
         <v>1202</v>
       </c>
       <c r="E10" s="2">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -23006,7 +23006,7 @@
         <v>1202</v>
       </c>
       <c r="E11" s="2">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -23025,7 +23025,7 @@
         <v>1202</v>
       </c>
       <c r="E12" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -23044,7 +23044,7 @@
         <v>1202</v>
       </c>
       <c r="E13" s="2">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -23126,7 +23126,7 @@
         <v>1202</v>
       </c>
       <c r="E17" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -23145,7 +23145,7 @@
         <v>1202</v>
       </c>
       <c r="E18" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -23206,7 +23206,7 @@
         <v>1202</v>
       </c>
       <c r="E21" s="2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -23246,7 +23246,7 @@
         <v>1202</v>
       </c>
       <c r="E23" s="2">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -23265,7 +23265,7 @@
         <v>1202</v>
       </c>
       <c r="E24" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -23284,7 +23284,7 @@
         <v>1202</v>
       </c>
       <c r="E25" s="2">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -23303,7 +23303,7 @@
         <v>1202</v>
       </c>
       <c r="E26" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -23322,7 +23322,7 @@
         <v>1202</v>
       </c>
       <c r="E27" s="2">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -23341,7 +23341,7 @@
         <v>1202</v>
       </c>
       <c r="E28" s="2">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -23360,7 +23360,7 @@
         <v>1202</v>
       </c>
       <c r="E29" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -23421,7 +23421,7 @@
         <v>1202</v>
       </c>
       <c r="E32" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -23461,7 +23461,7 @@
         <v>1202</v>
       </c>
       <c r="E34" s="2">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -23480,7 +23480,7 @@
         <v>1202</v>
       </c>
       <c r="E35" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -23583,7 +23583,7 @@
         <v>1202</v>
       </c>
       <c r="E40" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -23602,7 +23602,7 @@
         <v>1202</v>
       </c>
       <c r="E41" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -23621,7 +23621,7 @@
         <v>1202</v>
       </c>
       <c r="E42" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -23640,7 +23640,7 @@
         <v>1202</v>
       </c>
       <c r="E43" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -23764,7 +23764,7 @@
         <v>1202</v>
       </c>
       <c r="E49" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -23783,7 +23783,7 @@
         <v>1202</v>
       </c>
       <c r="E50" s="2">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
@@ -23823,7 +23823,7 @@
         <v>1202</v>
       </c>
       <c r="E52" s="2">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -23926,7 +23926,7 @@
         <v>1202</v>
       </c>
       <c r="E57" s="2">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -23945,7 +23945,7 @@
         <v>1202</v>
       </c>
       <c r="E58" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -23964,7 +23964,7 @@
         <v>1202</v>
       </c>
       <c r="E59" s="2">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -24025,7 +24025,7 @@
         <v>1202</v>
       </c>
       <c r="E62" s="2">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -24044,7 +24044,7 @@
         <v>1202</v>
       </c>
       <c r="E63" s="2">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -24063,7 +24063,7 @@
         <v>1202</v>
       </c>
       <c r="E64" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -24103,7 +24103,7 @@
         <v>1202</v>
       </c>
       <c r="E66" s="2">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
@@ -24122,7 +24122,7 @@
         <v>1202</v>
       </c>
       <c r="E67" s="2">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -24141,7 +24141,7 @@
         <v>1202</v>
       </c>
       <c r="E68" s="2">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -24160,7 +24160,7 @@
         <v>1202</v>
       </c>
       <c r="E69" s="2">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -24221,7 +24221,7 @@
         <v>1202</v>
       </c>
       <c r="E72" s="2">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -24240,7 +24240,7 @@
         <v>1202</v>
       </c>
       <c r="E73" s="2">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -24259,7 +24259,7 @@
         <v>1202</v>
       </c>
       <c r="E74" s="2">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -24341,7 +24341,7 @@
         <v>1202</v>
       </c>
       <c r="E78" s="2">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -24360,7 +24360,7 @@
         <v>1202</v>
       </c>
       <c r="E79" s="2">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -24400,7 +24400,7 @@
         <v>1202</v>
       </c>
       <c r="E81" s="2">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -24440,7 +24440,7 @@
         <v>1202</v>
       </c>
       <c r="E83" s="2">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -24522,7 +24522,7 @@
         <v>1202</v>
       </c>
       <c r="E87" s="2">
-        <v>68</v>
+        <v>210</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -24646,7 +24646,7 @@
         <v>1202</v>
       </c>
       <c r="E93" s="2">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -24686,7 +24686,7 @@
         <v>1202</v>
       </c>
       <c r="E95" s="2">
-        <v>56</v>
+        <v>203</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -24831,7 +24831,7 @@
         <v>1202</v>
       </c>
       <c r="E102" s="2">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -24913,7 +24913,7 @@
         <v>1202</v>
       </c>
       <c r="E106" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -24932,7 +24932,7 @@
         <v>1202</v>
       </c>
       <c r="E107" s="2">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -24951,7 +24951,7 @@
         <v>1205</v>
       </c>
       <c r="E108" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -24970,7 +24970,7 @@
         <v>1202</v>
       </c>
       <c r="E109" s="2">
-        <v>157</v>
+        <v>296</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
@@ -24989,7 +24989,7 @@
         <v>1202</v>
       </c>
       <c r="E110" s="2">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
@@ -25008,7 +25008,7 @@
         <v>1205</v>
       </c>
       <c r="E111" s="2">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
@@ -25027,7 +25027,7 @@
         <v>1202</v>
       </c>
       <c r="E112" s="2">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
@@ -25046,7 +25046,7 @@
         <v>1202</v>
       </c>
       <c r="E113" s="2">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -25065,7 +25065,7 @@
         <v>1202</v>
       </c>
       <c r="E114" s="2">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -25084,7 +25084,7 @@
         <v>1202</v>
       </c>
       <c r="E115" s="2">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -25103,7 +25103,7 @@
         <v>1202</v>
       </c>
       <c r="E116" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -25122,7 +25122,7 @@
         <v>1202</v>
       </c>
       <c r="E117" s="2">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -25141,7 +25141,7 @@
         <v>1202</v>
       </c>
       <c r="E118" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -25160,7 +25160,7 @@
         <v>1202</v>
       </c>
       <c r="E119" s="2">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -25179,7 +25179,7 @@
         <v>1205</v>
       </c>
       <c r="E120" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -25217,7 +25217,7 @@
         <v>1202</v>
       </c>
       <c r="E122" s="2">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
